--- a/Gallup__1970/Gallup__1970_registry_rows.xlsx
+++ b/Gallup__1970/Gallup__1970_registry_rows.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="R2c48c8719f824bf8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R02228eb19faa498c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rf6e92ecd034a4401"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source list" sheetId="1" r:id="Rc95c36d44ef148e4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Registry_rows" sheetId="2" r:id="R6e2de5bd5b024cb4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HOW_TO_PASTE" sheetId="3" r:id="Rd04319564dda4f08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -333,7 +333,7 @@
         <x:v>Mark-directed responses and spontaneous mirror-guided behaviour</x:v>
       </x:c>
       <x:c r="C2" s="3" t="str">
-        <x:v>Results / figures / tables: item selection pending</x:v>
+        <x:v>Figure 4: Chimpanzee mark-directed responses before and during mirror exposure</x:v>
       </x:c>
       <x:c r="D2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap
@@ -350,13 +350,13 @@
         <x:v>Nick/Fran dissertation reference check; existing source citation and protocol notes.</x:v>
       </x:c>
       <x:c r="H2" s="3" t="str">
-        <x:v>Unresolved — full text needed before assigning an item number</x:v>
+        <x:v>Verified in EndNote full text — PDF p. 2 / printed p. 87. Distinguish experimental and control animals. The filename says Gallop but the paper author is Gordon G. Gallup Jr.; the PDF also contains parts of adjacent Science articles. The lunar-rock Table 1 on this page is unrelated.</x:v>
       </x:c>
       <x:c r="I2" s="3" t="str">
-        <x:v>Full text not obtained — item cannot yet be verified</x:v>
+        <x:v>Existing full-text PDF verified in EndNote; original retained</x:v>
       </x:c>
       <x:c r="J2" s="3" t="str">
-        <x:v>Not obtained</x:v>
+        <x:v>/Users/crossmodal/Documents/References.Data/PDF/1101513895/Gallop-1970-Chimpanzees_ self-recognition.pdf</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -508,13 +508,15 @@
         <x:v>Human visual check of snapshot</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="190" customHeight="1">
+    <x:row r="2" ht="200" customHeight="1">
       <x:c r="A2" s="3" t="str">
         <x:v>Gallup, G. G., Jr. (1970). Chimpanzees: Self-Recognition. Science, 167(3914), 86–87. https://doi.org/10.1126/science.167.3914.86</x:v>
       </x:c>
       <x:c r="B2" s="6"/>
       <x:c r="C2" s="3"/>
-      <x:c r="D2" s="3"/>
+      <x:c r="D2" s="3" t="str">
+        <x:v>Figure 4</x:v>
+      </x:c>
       <x:c r="E2" s="6"/>
       <x:c r="F2" s="6"/>
       <x:c r="G2" s="6"/>
@@ -525,11 +527,11 @@
       <x:c r="L2" s="6"/>
       <x:c r="M2" s="6"/>
       <x:c r="N2" s="3" t="str">
-        <x:v>Article tables/figures/text (not extracted)</x:v>
+        <x:v>Existing EndNote full-text PDF verified; no dataset extraction</x:v>
       </x:c>
       <x:c r="O2" s="3" t="str">
         <x:v>Assistant mirror-literature addition; not found in dissertation references. Planned folder: Gallup__1970. Target: Results / figures / tables: item selection pending. Foundational chimpanzee experiment with monkey comparison. Extract observations and controls per subject and condition; the existing Gallup__1977 review is secondary to this experiment.
-Item check 2026-10-25: Unresolved — full text needed before assigning an item number. Availability: Full text not obtained — item cannot yet be verified.</x:v>
+EndNote check 2026-10-25: Verified in EndNote full text — PDF p. 2 / printed p. 87. Distinguish experimental and control animals. The filename says Gallop but the paper author is Gordon G. Gallup Jr.; the PDF also contains parts of adjacent Science articles. The lunar-rock Table 1 on this page is unrelated. Local PDF: /Users/crossmodal/Documents/References.Data/PDF/1101513895/Gallop-1970-Chimpanzees_ self-recognition.pdf</x:v>
       </x:c>
       <x:c r="P2" s="3" t="str">
         <x:v>HOLD — primary evidence only for a demonstrated gap</x:v>
@@ -550,7 +552,7 @@
         <x:v>Primates</x:v>
       </x:c>
       <x:c r="X2" s="3" t="str">
-        <x:v>Mark-directed responses and spontaneous mirror-guided behaviour</x:v>
+        <x:v>Chimpanzee mark-directed responses before and during mirror exposure</x:v>
       </x:c>
       <x:c r="Y2" s="3"/>
       <x:c r="Z2" s="3"/>
@@ -703,7 +705,7 @@
         <x:v>Source files</x:v>
       </x:c>
       <x:c r="B15" s="3" t="str">
-        <x:v>Acquired PDFs, full-text HTML and original Kerney supplements are stored in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. README.md in each source folder gives complete paths and verification details. Kowianski 1999 uses an existing PDF in the teaching archive.</x:v>
+        <x:v>EndNote PDFs are linked by full path in Source list and source-folder README files; originals remain unchanged. Earlier downloads remain in /Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Evo-M1-Trait-Data-restricted/source_library/Nick_Fran_2026-10-25. Kowianski 1999 remains in the teaching archive. File availability does not establish new data.</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="100" customHeight="1">
@@ -711,7 +713,7 @@
         <x:v>Unresolved items</x:v>
       </x:c>
       <x:c r="B16" s="3" t="str">
-        <x:v>Blank Item number means either full text is still required or a review is REFERENCE ONLY. Smaers 2013 Table 1 is retained from earlier identification but has not been reverified from a locally acquired full text. Human snapshot checks remain pending.</x:v>
+        <x:v>All 29 candidate full texts are now available. Blank Item number remains intentional for reference-only reviews and for Nunn 2001, whose group-composition input database is not printed in the paper. Results Text is a descriptive source locus, not a printed table number. No data extraction, deduplication or human snapshot check has been completed.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -995,13 +997,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{247E799B-06E9-44F4-AF6B-6BFE599C1F9A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FE632672-9D97-4928-A43E-BA5751B2B57A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E62789F4-4718-4485-BE6C-030D6F917B1E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3B6DBB22-7B53-4D88-9949-B40F54B891A2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{351F65D7-76B0-49B7-BF9E-2D3EFA95353F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9128CED2-0068-404F-8A4F-82D5157EBAE7}"/>
 </file>